--- a/data/credit_bond_all_2026-09-09.xlsx
+++ b/data/credit_bond_all_2026-09-09.xlsx
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="V50" s="4" t="n">
         <v>1.5</v>
@@ -11816,7 +11816,7 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26江铜股份MTN004A(并购)</t>
+          <t>26长沙水业MTN003</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11826,12 +11826,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>102683574.IB</t>
+          <t>102683570.IB</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -11842,48 +11842,48 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.11</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>41.84</v>
+        <v>52.94</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26江铜股份MTN003A(并购)</t>
+          <t>26长沙水业MTN001</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>9.96Y</t>
+          <t>2.88Y+N</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>2.1088</t>
+          <t>1.7717</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>2.1200/2.1100</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>江西铜业股份有限公司</t>
+          <t>长沙水业集团有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.28</t>
+          <t>C 29.92</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11907,40 +11907,38 @@
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V51" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>4.82</v>
+      </c>
+      <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>江西省-鹰潭市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行金额为人民币10亿元,发行规模上限为人民币15亿元,募集资金12亿元拟用于补充发行人一年内以自有资金出资并购项目而产生的资金缺口,募集后的资金拟用于补充营运资金、偿还有息债务等,募集资金3亿元拟用于偿还公司存量有息债务。</t>
+          <t>本期中期票据拟募集资金5亿元,所募集资金拟用于偿还发行人存量债务融资工具[23长沙水业MTN004]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,北京银行股份有限公司</t>
+          <t>招商银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
@@ -11961,7 +11959,7 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>江西铜业股份有限公司2026年度第四期中期票据(并购)(品种一)</t>
+          <t>长沙水业集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11971,7 +11969,7 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2036-09-10</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK51" s="3"/>
@@ -11992,32 +11990,32 @@
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -12032,7 +12030,7 @@
       </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX51" s="3" t="inlineStr">
@@ -12045,81 +12043,79 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ51" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ51" s="3"/>
     </row>
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26长沙水业MTN003</t>
+          <t>26桂铁07</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>102683570.IB</t>
+          <t>524938.SZ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>52.94</v>
+        <v>33.03</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26长沙水业MTN001</t>
+          <t>26桂铁05</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.88Y+N</t>
+          <t>2.93Y+2.00Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7717</t>
+          <t>1.7438</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>1.8100/--</t>
+          <t>1.7500/1.7100</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>长沙水业集团有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C 29.92</t>
+          <t>B- 44.35</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12129,7 +12125,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12139,48 +12135,48 @@
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>4.82</v>
+        <v>4.18</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟募集资金5亿元,所募集资金拟用于偿还发行人存量债务融资工具[23长沙水业MTN004]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁03]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,财信证券股份有限公司</t>
+          <t>东方证券股份有限公司,平安证券股份有限公司,兴业证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
@@ -12190,12 +12186,12 @@
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>长沙水业集团有限公司2026年度第三期中期票据</t>
+          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12205,25 +12201,25 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>类城投</t>
@@ -12231,32 +12227,32 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV52" s="3" t="inlineStr">
@@ -12266,7 +12262,7 @@
       </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX52" s="3" t="inlineStr">
@@ -12284,22 +12280,22 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>26舟山海投MTN001</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>524938.SZ</t>
+          <t>102683531.IB</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -12310,48 +12306,48 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.35 ~ 2.35</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>33.03</v>
+        <v>33.74</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26桂铁05</t>
+          <t>26舟投01</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+2.00Y</t>
+          <t>4.77Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7438</t>
+          <t>1.8357</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>舟山海洋投资集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>B- 44.35</t>
+          <t>D- 2.50</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12361,7 +12357,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 14:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12375,17 +12371,17 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -12396,23 +12392,23 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁03]</t>
+          <t>发行人本次中期票据注册规模为 20.00 亿元，本期发行金额 10.00 亿元，募集资金拟全部用于偿还发行人子公司债务融资工具到期本金。 [23 舟山海洋MTN001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,平安证券股份有限公司,兴业证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
@@ -12422,12 +12418,12 @@
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>舟山海洋投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12443,54 +12439,54 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>渔业</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM53" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO53" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ53" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR53" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-11</t>
-        </is>
-      </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -12498,7 +12494,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12508,7 +12504,7 @@
       </c>
       <c r="AY53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AZ53" s="3"/>
@@ -12516,7 +12512,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26舟山海投MTN001</t>
+          <t>26粤铁建MTN005</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12526,12 +12522,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102683531.IB</t>
+          <t>102683578.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -12542,48 +12538,48 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 2.35</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>33.74</v>
+        <v>34.94</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26舟投01</t>
+          <t>26粤铁建MTN004</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>4.77Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.8357</t>
+          <t>1.6887</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6850/1.6600</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>舟山海洋投资集团有限公司</t>
+          <t>广东省铁路建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>B- 47.31</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12593,7 +12589,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-09 14:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12607,17 +12603,19 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="V54" s="3"/>
+        <v>3.72</v>
+      </c>
+      <c r="V54" s="4" t="n">
+        <v>3.77</v>
+      </c>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -12628,17 +12626,13 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
-        </is>
-      </c>
-      <c r="AB54" s="3" t="inlineStr">
-        <is>
-          <t>发行人本次中期票据注册规模为 20.00 亿元，本期发行金额 10.00 亿元，募集资金拟全部用于偿还发行人子公司债务融资工具到期本金。 [23 舟山海洋MTN001]</t>
-        </is>
-      </c>
+          <t>广东省</t>
+        </is>
+      </c>
+      <c r="AB54" s="3"/>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,宁波银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12659,7 +12653,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>舟山海洋投资集团有限公司2026年度第一期中期票据</t>
+          <t>广东省铁路建设投资集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12669,7 +12663,7 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
@@ -12680,7 +12674,7 @@
       </c>
       <c r="AM54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN54" s="3" t="inlineStr">
@@ -12690,32 +12684,32 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>渔业</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12748,7 +12742,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN005</t>
+          <t>26北部湾MTN007B</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12758,64 +12752,64 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102683578.IB</t>
+          <t>102683567.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>34.94</v>
+        <v>47.74</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN004</t>
+          <t>26北部湾MTN006B</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.83Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.6887</t>
+          <t>1.9634</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.6850/1.6600</t>
+          <t>1.9800/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司</t>
+          <t>广西北部湾国际港务集团有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>B- 47.31</t>
+          <t>C- 20.62</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12839,19 +12833,17 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="V55" s="4" t="n">
-        <v>3.77</v>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -12862,13 +12854,17 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>广东省</t>
-        </is>
-      </c>
-      <c r="AB55" s="3"/>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，拟用于发行人偿还到期债务[23北部湾MTN004]</t>
+        </is>
+      </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信证券股份有限公司</t>
+          <t>国家开发银行,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -12889,7 +12885,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司2026年度第五期中期票据</t>
+          <t>广西北部湾国际港务集团有限公司2026年度第七期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12899,7 +12895,7 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
@@ -12910,7 +12906,7 @@
       </c>
       <c r="AM55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -12920,12 +12916,12 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
@@ -12935,17 +12931,17 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -12978,7 +12974,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26北部湾MTN007B</t>
+          <t>26皖能股MTN004</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12988,64 +12984,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>102683567.IB</t>
+          <t>102683577.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.84 ~ 2.14</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>47.74</v>
+        <v>46.03</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26北部湾MTN006B</t>
+          <t>26皖能股MTN003</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>4.83Y</t>
+          <t>9.82Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.9634</t>
+          <t>2.1878</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.9800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司</t>
+          <t>安徽省皖能股份有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 20.62</t>
+          <t>C- 18.72</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13069,17 +13065,19 @@
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V56" s="3"/>
+        <v>1.11</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -13090,17 +13088,17 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，拟用于发行人偿还到期债务[23北部湾MTN004]</t>
+          <t>本期中期票据发行金额9亿元,拟用于发行人及子公司日常经营补充流动资金及偿还发行人及子公司存量有息债务。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行,中国农业银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13121,7 +13119,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司2026年度第七期中期票据(品种二)</t>
+          <t>安徽省皖能股份有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -13131,7 +13129,7 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -13142,7 +13140,7 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
@@ -13157,27 +13155,27 @@
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -13210,59 +13208,59 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26皖能股MTN004</t>
+          <t>26碚科03</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>102683577.IB</t>
+          <t>283952.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.84 ~ 2.14</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>46.03</v>
+        <v>60.03</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26皖能股MTN003</t>
+          <t>26缙云01</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>9.82Y</t>
+          <t>4.37Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.1878</t>
+          <t>1.9502</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -13272,12 +13270,12 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>安徽省皖能股份有限公司</t>
+          <t>重庆北碚西部科学城投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 18.72</t>
+          <t>C- 16.24</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13287,7 +13285,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13301,46 +13299,44 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V57" s="4" t="n">
-        <v>1.26</v>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>2.02%~2.12%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>重庆市-北碚区</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额9亿元,拟用于发行人及子公司日常经营补充流动资金及偿还发行人及子公司存量有息债务。</t>
+          <t>本期债券发行规模为不超过3.00亿元(含3.00亿元),募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金。[23缙云02]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
+          <t>国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -13350,28 +13346,28 @@
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>安徽省皖能股份有限公司2026年度第四期中期票据</t>
+          <t>重庆北碚西部科学城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM57" s="3" t="inlineStr">
@@ -13386,32 +13382,32 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13436,7 +13432,7 @@
       </c>
       <c r="AY57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AZ57" s="3"/>
@@ -13444,7 +13440,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26碚科03</t>
+          <t>26中泰05</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13454,125 +13450,129 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>283952.SH</t>
+          <t>246007.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3.0</v>
+        <v>30.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>60.03</v>
+        <v>41.94</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>26中泰04</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>2.93Y</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>1.6561</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>1.6600/1.6500</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>中泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.31</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>26缙云01</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>4.37Y</t>
-        </is>
-      </c>
-      <c r="M58" s="3" t="inlineStr">
-        <is>
-          <t>1.9502</t>
-        </is>
-      </c>
-      <c r="N58" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>重庆北碚西部科学城投资发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="inlineStr">
-        <is>
-          <t>C- 16.24</t>
-        </is>
-      </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>09-09 15:00</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>2.02%~2.12%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z58" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>重庆市-北碚区</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过3.00亿元(含3.00亿元),募集资金扣除发行费用后,拟全部用于偿还回售的公司债券本金。[23缙云02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不超过15亿元(含)用于置换公司偿还到期公司债券本金的自有资金;不超过15亿元(含)用于补充公司流动资金,满足公司业务运营需要。[21中泰03]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13587,17 +13587,17 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>重庆北碚西部科学城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13618,32 +13618,32 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13676,7 +13676,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26中泰05</t>
+          <t>25浙能K2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13686,64 +13686,58 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>246007.SH</t>
+          <t>242734.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
+        <v>6.0</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="4" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>41.94</v>
+        <v>46.84</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26中泰04</t>
+          <t>24浙能源MTN001</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>7.49Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.6561</t>
+          <t>1.9068</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6500</t>
+          <t>--/1.8800</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司</t>
+          <t>浙江省能源集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>B- 40.31</t>
+          <t>C- 21.86</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13753,7 +13747,7 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -13763,21 +13757,19 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U59" s="4" t="n">
-        <v>3.22</v>
-      </c>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.95%~2.15%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13792,23 +13784,23 @@
       </c>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不超过15亿元(含)用于置换公司偿还到期公司债券本金的自有资金;不超过15亿元(含)用于补充公司流动资金,满足公司业务运营需要。[21中泰03]</t>
+          <t>本期债券募集资金扣除发行费用后，拟将全部用于偿还到期的中期票据本金【22 浙能源 MTN001】</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
@@ -13823,7 +13815,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司2026年面向专业投资者公开发行公司债券(第五期)</t>
+          <t>浙江省能源集团有限公司2025年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13833,18 +13825,22 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
-        </is>
-      </c>
-      <c r="AK59" s="3"/>
+          <t>2035-04-14</t>
+        </is>
+      </c>
+      <c r="AK59" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL59" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AM59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AN59" s="3" t="inlineStr">
@@ -13854,32 +13850,32 @@
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13912,7 +13908,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>25浙能K2</t>
+          <t>26青信12</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13922,7 +13918,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>242734.SH</t>
+          <t>246029.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -13931,49 +13927,55 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
       <c r="H60" s="4" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>46.84</v>
+        <v>69.84</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>24浙能源MTN001</t>
+          <t>26青岛国信MTN008B</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>7.49Y</t>
+          <t>9.96Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.9068</t>
+          <t>2.3856</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/1.8800</t>
+          <t>--/2.3500</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>浙江省能源集团有限公司</t>
+          <t>青岛国信发展(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 21.86</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13993,19 +13995,19 @@
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.15%</t>
+          <t>2.31%~2.41%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -14013,24 +14015,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z60" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，拟将全部用于偿还到期的中期票据本金【22 浙能源 MTN001】</t>
+          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -14051,7 +14049,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>浙江省能源集团有限公司2025年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
+          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14061,22 +14059,18 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2035-04-14</t>
-        </is>
-      </c>
-      <c r="AK60" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2036-09-11</t>
+        </is>
+      </c>
+      <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t/>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN60" s="3" t="inlineStr">
@@ -14086,32 +14080,32 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14144,7 +14138,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26青信12</t>
+          <t>26中金11</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14154,64 +14148,64 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>246029.SH</t>
+          <t>246040.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+3</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.5</v>
+        <v>30.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>7.0</v>
+        <v>21.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>69.84</v>
+        <v>16.0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>26青岛国信MTN008B</t>
+          <t>26中金K3</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>9.96Y</t>
+          <t>2.86Y+2.00Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2.3856</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/2.3500</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>B- 41.87</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14221,7 +14215,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -14234,16 +14228,18 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U61" s="3"/>
+      <c r="U61" s="4" t="n">
+        <v>4.48</v>
+      </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>2.31%~2.41%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
@@ -14251,31 +14247,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z61" s="3"/>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换已偿还到期公司债券本金的自有资金[21青纾01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将10亿元用于置换公司债券本金,50亿元用于补充流动资金。[23中金F1]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>青岛国信发展(集团)有限责任公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
+          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14295,10 +14295,14 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
-        </is>
-      </c>
-      <c r="AK61" s="3"/>
+          <t>2032-09-11</t>
+        </is>
+      </c>
+      <c r="AK61" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
           <t/>
@@ -14306,7 +14310,7 @@
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
@@ -14316,37 +14320,37 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV61" s="3" t="inlineStr">
@@ -14356,7 +14360,7 @@
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
@@ -14374,7 +14378,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26中金11</t>
+          <t>26长城03</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14384,64 +14388,64 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>246040.SH</t>
+          <t>524996.SZ</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3+3</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>16.0</v>
+        <v>40.94</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>26中金K3</t>
+          <t>24长城06</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.86Y+2.00Y</t>
+          <t>2.85Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.6218</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.6330/--</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>B- 41.87</t>
+          <t>B- 38.99</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14465,17 +14469,17 @@
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>4.48</v>
+        <v>4.95</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -14490,17 +14494,17 @@
       </c>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将10亿元用于置换公司债券本金,50亿元用于补充流动资金。[23中金F1]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期债务。[23长城10,21长城08,23长城07]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14516,12 +14520,12 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种一)</t>
+          <t>长城证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14531,14 +14535,10 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2032-09-11</t>
-        </is>
-      </c>
-      <c r="AK62" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-11</t>
+        </is>
+      </c>
+      <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
           <t/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AU62" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV62" s="3" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="AW62" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX62" s="3" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26长城03</t>
+          <t>26联资05</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14624,64 +14624,64 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>524996.SZ</t>
+          <t>283884.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>40.94</v>
+        <v>39.03</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>24长城06</t>
+          <t>24联投资本PPN003B</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.85Y</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.6218</t>
+          <t>1.8836</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>1.6330/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>湖北联投资本投资发展有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>B- 38.99</t>
+          <t>C- 19.60</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14705,17 +14705,17 @@
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>4.95</v>
+        <v>3.7</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -14723,55 +14723,51 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z63" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期债务。[23长城10,21长城08,23长城07]</t>
+          <t>本期公司债券募集资金0.10亿元用于偿还到期债务,3.90亿元用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG63" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种一)</t>
+          <t>湖北联投资本投资发展有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14797,7 +14793,7 @@
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
@@ -14807,22 +14803,22 @@
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV63" s="3" t="inlineStr">
@@ -14832,7 +14828,7 @@
       </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX63" s="3" t="inlineStr">
@@ -14850,7 +14846,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26联资05</t>
+          <t>26沿海05</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14860,64 +14856,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>283884.SH</t>
+          <t>283934.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>39.03</v>
+        <v>48.03</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>24联投资本PPN003B</t>
+          <t>26沿海04</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.8836</t>
+          <t>1.8888</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>湖北联投资本投资发展有限公司</t>
+          <t>南通沿海开发集团有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 19.60</t>
+          <t>B- 36.82</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14927,7 +14923,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14941,17 +14937,17 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -14962,17 +14958,17 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金0.10亿元用于偿还到期债务,3.90亿元用于补充公司流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司将到期的公司债券本金[23沿海04]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,东方证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -14993,7 +14989,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>湖北联投资本投资发展有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种一)</t>
+          <t>南通沿海开发集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15024,37 +15020,37 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>其他休闲服务</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV64" s="3" t="inlineStr">
@@ -15064,7 +15060,7 @@
       </c>
       <c r="AW64" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX64" s="3" t="inlineStr">
@@ -15082,7 +15078,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26沿海05</t>
+          <t>26光证G6</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15092,64 +15088,64 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>283934.SH</t>
+          <t>246032.SH</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>48.03</v>
+        <v>33.79</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>26沿海04</t>
+          <t>26光证G5</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>4.83Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.8888</t>
+          <t>1.7202</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>1.9500/--</t>
+          <t>1.7750/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>B- 36.82</t>
+          <t>B 52.13</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15159,7 +15155,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -15173,49 +15169,49 @@
         </is>
       </c>
       <c r="U65" s="4" t="n">
-        <v>2.68</v>
+        <v>3.77</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X65" s="3" t="inlineStr">
-        <is>
-          <t>1.87%~1.97%</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X65" s="3"/>
       <c r="Y65" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z65" s="3"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还公司将到期的公司债券本金[23沿海04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金、补充流动资金；本期债券募集资金30亿元拟用于偿还到期公司债券本金；本期债券募集资金20亿元用于补充公司日常经营所需流动资金[26光证S1]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东方证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>兴业证券股份有限公司,招商证券股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG65" s="3" t="inlineStr">
@@ -15225,20 +15221,24 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>南通沿海开发集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>光大证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
-        </is>
-      </c>
-      <c r="AK65" s="3"/>
+          <t>2031-08-16</t>
+        </is>
+      </c>
+      <c r="AK65" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL65" s="3" t="inlineStr">
         <is>
           <t/>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AM65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN65" s="3" t="inlineStr">
@@ -15256,32 +15256,32 @@
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>其他休闲服务</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -15314,7 +15314,7 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26光证G6</t>
+          <t>26长城04</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15324,64 +15324,64 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>246032.SH</t>
+          <t>524997.SZ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>24.0</v>
+        <v>7.0</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>33.79</v>
+        <v>35.03</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>26光证G5</t>
+          <t>25长城04</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>4.83Y</t>
+          <t>4.00Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.7202</t>
+          <t>1.7089</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>1.7750/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>B 52.13</t>
+          <t>B- 38.99</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15405,15 +15405,19 @@
         </is>
       </c>
       <c r="U66" s="4" t="n">
-        <v>3.77</v>
+        <v>6.09</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X66" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -15426,17 +15430,17 @@
       </c>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金、补充流动资金；本期债券募集资金30亿元拟用于偿还到期公司债券本金；本期债券募集资金20亿元用于补充公司日常经营所需流动资金[26光证S1]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期债务。[23长城10,21长城08,23长城07]</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,招商证券股份有限公司,东方证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
@@ -15452,12 +15456,12 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>长城证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
@@ -15467,14 +15471,10 @@
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2031-08-16</t>
-        </is>
-      </c>
-      <c r="AK66" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-11</t>
+        </is>
+      </c>
+      <c r="AK66" s="3"/>
       <c r="AL66" s="3" t="inlineStr">
         <is>
           <t/>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AM66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN66" s="3" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
@@ -15550,7 +15550,7 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26长城04</t>
+          <t>G26浙租1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15560,64 +15560,64 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>524997.SZ</t>
+          <t>246016.SH</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
         <v>10.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>35.03</v>
+        <v>34.94</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>25长城04</t>
+          <t>24浙商租赁MTN001</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>4.00Y</t>
+          <t>253D</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.7089</t>
+          <t>1.5501</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5300</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>浙江浙商融资租赁有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>B- 38.99</t>
+          <t>D+ 8.33</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15641,17 +15641,17 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>6.09</v>
+        <v>3.88</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -15659,45 +15659,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z67" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期债务。[23长城10,21长城08,23长城07]</t>
+          <t>本期发行规模不超过10亿元(含10亿元),募集资金拟用于置换本期债券发行前12个月内发行人用于绿色项目租赁款投放的自有资金支出。</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF67" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG67" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司2026年面向专业投资者公开发行公司债券(第二期)(品种二)</t>
+          <t>浙江浙商融资租赁有限公司2026年面向专业投资者公开发行绿色公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15707,7 +15703,7 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
@@ -15733,7 +15729,7 @@
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
@@ -15743,17 +15739,17 @@
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
@@ -15786,74 +15782,74 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>G26浙租1</t>
+          <t>26宏河控股PPN001(并购)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>246016.SH</t>
+          <t>032680519.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.60 ~ 3.80</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1.6</v>
+        <v>2.95</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>34.94</v>
+        <v>154.03</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>24浙商租赁MTN001</t>
+          <t>26宏河02</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>253D</t>
+          <t>6.63Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1.5501</t>
+          <t>3.8210</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/1.5300</t>
+          <t>--/3.5000</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>浙江浙商融资租赁有限公司</t>
+          <t>山东宏河控股集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.33</t>
+          <t>C 27.97</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15863,7 +15859,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -15873,48 +15869,48 @@
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U68" s="4" t="n">
-        <v>3.88</v>
+        <v>1.5</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.56%~2.66%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期发行规模不超过10亿元(含10亿元),募集资金拟用于置换本期债券发行前12个月内发行人用于绿色项目租赁款投放的自有资金支出。</t>
+          <t>本次定向债务融资工具基础发行规模0亿元,发行规模上限6亿元。其中5亿元用于未来拟付的并购款项,1亿元用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,浙商证券股份有限公司</t>
+          <t>青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
@@ -15924,28 +15920,28 @@
       </c>
       <c r="AG68" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>浙江浙商融资租赁有限公司2026年面向专业投资者公开发行绿色公司债券(第一期)</t>
+          <t>山东宏河控股集团有限公司2026年度第一期定向债务融资工具(并购)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM68" s="3" t="inlineStr">
@@ -15955,42 +15951,42 @@
       </c>
       <c r="AN68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV68" s="3" t="inlineStr">
@@ -16000,7 +15996,7 @@
       </c>
       <c r="AW68" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX68" s="3" t="inlineStr">
@@ -16018,7 +16014,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26宏河控股PPN001(并购)</t>
+          <t>26江铜股份MTN004A(并购)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -16028,64 +16024,64 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>032680519.IB</t>
+          <t>102683574.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2.60 ~ 3.80</t>
+          <t>1.90 ~ 2.11</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>154.03</v>
+        <v>41.84</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26宏河02</t>
+          <t>26江铜股份MTN003A(并购)</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>6.63Y</t>
+          <t>9.96Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>3.8210</t>
+          <t>2.1088</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/3.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>山东宏河控股集团有限公司</t>
+          <t>江西铜业股份有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C 27.97</t>
+          <t>B+ 57.28</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16109,44 +16105,46 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V69" s="3"/>
+        <v>1.24</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>2.56%~2.66%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>江西省-鹰潭市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具基础发行规模0亿元,发行规模上限6亿元。其中5亿元用于未来拟付的并购款项,1亿元用于偿还有息债务。</t>
+          <t>本期中期票据基础发行金额为人民币10亿元,发行规模上限为人民币15亿元,募集资金12亿元拟用于补充发行人一年内以自有资金出资并购项目而产生的资金缺口,募集后的资金拟用于补充营运资金、偿还有息债务等,募集资金3亿元拟用于偿还公司存量有息债务。</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>青岛银行股份有限公司</t>
+          <t>中信银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16161,17 +16159,17 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>山东宏河控股集团有限公司2026年度第一期定向债务融资工具(并购)</t>
+          <t>江西铜业股份有限公司2026年度第四期中期票据(并购)(品种一)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2036-09-10</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
@@ -16197,32 +16195,32 @@
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV69" s="3" t="inlineStr">
@@ -16232,7 +16230,7 @@
       </c>
       <c r="AW69" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX69" s="3" t="inlineStr">
@@ -16245,7 +16243,9 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ69" s="3"/>
+      <c r="AZ69" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-09.xlsx
+++ b/data/credit_bond_all_2026-09-09.xlsx
@@ -2290,7 +2290,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26中金12</t>
+          <t>26建集Y5</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2300,64 +2300,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>246041.SH</t>
+          <t>246013.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>30.0</v>
+        <v>8.5</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>14.11</v>
+        <v>73.94</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26中金K4</t>
+          <t>24建集Y4</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.86Y+2.00Y</t>
+          <t>2.94Y+N</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6995</t>
+          <t>2.0247</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>厦门建发集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 43.06</t>
+          <t>B- 36.59</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2377,21 +2377,21 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.38</v>
+        <v>2.14</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2399,35 +2399,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将10亿元用于置换公司债券本金,50亿元用于补充流动资金。[23中金F1]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换已用于偿还到期公司债券本金的自有资金。[23建集Y3,21建集01]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信证券股份有限公司,兴业证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2437,7 +2433,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
+          <t>厦门建发集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)(品种一)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2447,58 +2443,58 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2034-09-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2508,7 +2504,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2526,74 +2522,74 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26昆北01</t>
+          <t>26核风电GN007(乡村振兴)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>283863.SH</t>
+          <t>132680094.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.92Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>61.03</v>
+        <v>18.09</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26沪苏01</t>
+          <t>24风电GVK1</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.69Y</t>
+          <t>317D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.9175</t>
+          <t>1.4996</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>昆山北部新城集团有限公司</t>
+          <t>中广核风电有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>D- 1.50</t>
+          <t>C 25.76</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2603,7 +2599,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2613,79 +2609,79 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.35</v>
+        <v>3.1267</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还公司债券本金[24昆北01]</t>
+          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人在帆石二期、贵州龙里草原风电场项目、贵州都匀青峰(149.8MW)风电场项目3个绿色项目上三个月内的自有资金支出；其中8亿元募集资金拟用于乡村振兴领域，涉及贵州龙里草原风电场项目3.00亿元、贵州都匀青峰(149.8MW)风电场项目5.00亿元</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>昆山北部新城集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中广核风电有限公司2026年度第七期绿色短期融资券(乡村振兴)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2027-08-10</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2695,37 +2691,37 @@
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>7.5*无效</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>环保工程及服务</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2758,59 +2754,59 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26建集Y5</t>
+          <t>26三峡文旅SCP003</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>246013.SH</t>
+          <t>012682225.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.5</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>73.94</v>
+        <v>45.31</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24建集Y4</t>
+          <t>26三峡文旅SCP002</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.94Y+N</t>
+          <t>251D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.0247</t>
+          <t>1.7034</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2820,12 +2816,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>厦门建发集团有限公司</t>
+          <t>湖北三峡文化旅游集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 36.59</t>
+          <t>B- 36.43</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2835,7 +2831,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 11:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2845,48 +2841,48 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.67%~1.71%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>湖北省-宜昌市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于置换已用于偿还到期公司债券本金的自有资金。[23建集Y3,21建集01]</t>
+          <t>本次超短期融资券注册金额为20亿元,基础发行规模0亿元,发行金额上限为5亿元,募集资金拟用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,兴业证券股份有限公司,中国国际金融股份有限公司,平安证券股份有限公司</t>
+          <t>兴业证券股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2896,12 +2892,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>厦门建发集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)(品种一)</t>
+          <t>湖北三峡文化旅游集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2911,60 +2907,60 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>贸易零售</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2972,7 +2968,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2990,7 +2986,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26核风电GN007(乡村振兴)</t>
+          <t>26鄂交投MTN001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3000,64 +2996,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>132680094.IB</t>
+          <t>102683568.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.92Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>18.09</v>
+        <v>30.03</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>24风电GVK1</t>
+          <t>26鄂交投债02</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>317D</t>
+          <t>4.74Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4996</t>
+          <t>1.7399</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司</t>
+          <t>湖北交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 25.76</t>
+          <t>C+ 31.42</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3067,7 +3063,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 10:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3081,9 +3077,11 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.1267</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>4.51</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>2.28</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -3091,7 +3089,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3102,28 +3100,28 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人在帆石二期、贵州龙里草原风电场项目、贵州都匀青峰(149.8MW)风电场项目3个绿色项目上三个月内的自有资金支出；其中8亿元募集资金拟用于乡村振兴领域，涉及贵州龙里草原风电场项目3.00亿元、贵州都匀青峰(149.8MW)风电场项目5.00亿元</t>
+          <t>本期发行金额为20.00亿元,拟偿还有息债务[26鄂交投SCP003,23鄂交投MTN003]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中国农业银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国农业银行股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -3133,7 +3131,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司2026年度第七期绿色短期融资券(乡村振兴)</t>
+          <t>湖北交通投资集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3143,7 +3141,7 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-08-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3164,32 +3162,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3222,7 +3220,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26三峡文旅SCP003</t>
+          <t>26核风电GN008</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3232,64 +3230,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>012682225.IB</t>
+          <t>132680095.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.92Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.33 ~ 1.53</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>45.31</v>
+        <v>18.09</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26三峡文旅SCP002</t>
+          <t>24风电GVK1</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>251D</t>
+          <t>317D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7034</t>
+          <t>1.4996</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>湖北三峡文化旅游集团有限公司</t>
+          <t>中广核风电有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 36.43</t>
+          <t>C 25.76</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3299,7 +3297,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-09 11:00</t>
+          <t>09-09 14:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3313,49 +3311,51 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>1.9</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.83</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.71%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>湖北省-宜昌市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次超短期融资券注册金额为20亿元,基础发行规模0亿元,发行金额上限为5亿元,募集资金拟用于偿还有息负债</t>
+          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人三个月内在帆石一期、贵州龙里坪子风电场项目、大嘎吉20万千瓦光伏3个绿色项目建设运营的自有资金支出</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司,兴业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>湖北三峡文化旅游集团有限公司2026年度第三期超短期融资券</t>
+          <t>中广核风电有限公司2026年度第八期绿色短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2027-08-10</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3396,32 +3396,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3454,74 +3454,74 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26鄂交投MTN001</t>
+          <t>26环城01</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683568.IB</t>
+          <t>283941.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20.0</v>
+        <v>3.4</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>20.0</v>
+        <v>3.4</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30.03</v>
+        <v>49.03</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26鄂交投债02</t>
+          <t>24环城02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.74Y</t>
+          <t>348D+2.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7399</t>
+          <t>1.8258</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司</t>
+          <t>天津环城城市基础设施投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.42</t>
+          <t>C- 18.55</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-09 10:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3545,46 +3545,40 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>2.28</v>
-      </c>
+        <v>4.8824</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X15" s="3"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>湖北省</t>
+          <t>天津市-西青区</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为20.00亿元,拟偿还有息债务[26鄂交投SCP003,23鄂交投MTN003]</t>
+          <t>本期债券募集资金3.40亿元拟用于全部用于偿还回售的公司债本金[23环城01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国农业银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3594,17 +3588,17 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>湖北交通投资集团有限公司2026年度第一期中期票据</t>
+          <t>天津环城城市基础设施投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
@@ -3615,12 +3609,12 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3635,7 +3629,7 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3645,22 +3639,22 @@
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3670,7 +3664,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3688,74 +3682,74 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26核风电GN008</t>
+          <t>26泸建01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>132680095.IB</t>
+          <t>283892.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.92Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>18.09</v>
+        <v>69.03</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>24风电GVK1</t>
+          <t>24泸州城投PPN002</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>317D</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.4996</t>
+          <t>2.1108</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司</t>
+          <t>泸州市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 25.76</t>
+          <t>C- 10.44</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3765,7 +3759,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-09 14:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3779,82 +3773,80 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.83</v>
-      </c>
+        <v>4.95</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>1.46%~1.50%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X16" s="3"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-泸州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期绿色短期融资券15亿元募集资金拟用于置换发行人三个月内在帆石一期、贵州龙里坪子风电场项目、大嘎吉20万千瓦光伏3个绿色项目建设运营的自有资金支出</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23泸建01,23泸建02]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>国泰海通证券股份有限公司,华西证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>泸州两江投资控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>中广核风电有限公司2026年度第八期绿色短期融资券</t>
+          <t>泸州市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-08-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
@@ -3864,32 +3856,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3899,7 +3891,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3922,7 +3914,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26环城01</t>
+          <t>26HPI03K</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3932,64 +3924,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283941.SH</t>
+          <t>246046.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.4</v>
+        <v>15.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>49.03</v>
+        <v>26.84</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24环城02</t>
+          <t>25华能MTN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>348D+2.00Y</t>
+          <t>8.35Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.8258</t>
+          <t>1.9819</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.9300</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>天津环城城市基础设施投资集团有限公司</t>
+          <t>华能国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 18.55</t>
+          <t>B- 41.24</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4013,34 +4005,42 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.8824</v>
+        <v>2.9867</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X17" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z17" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>天津市-西青区</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3.40亿元拟用于全部用于偿还回售的公司债本金[23环城01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,兴业证券股份有限公司,西南证券股份有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4061,28 +4061,28 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>天津环城城市基础设施投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>华能国际电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2036-09-10</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4092,37 +4092,37 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4150,22 +4150,22 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26泸建01</t>
+          <t>26中兵投资SCP002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283892.SH</t>
+          <t>012682226.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -4176,48 +4176,48 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.33 ~ 1.53</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>69.03</v>
+        <v>31.49</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24泸州城投PPN002</t>
+          <t>24中兵01</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>254D+2.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.1108</t>
+          <t>1.5406</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5100</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>泸州市城市建设投资集团有限公司</t>
+          <t>中兵投资管理有限责任公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 10.44</t>
+          <t>C+ 33.85</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 11:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4241,215 +4241,219 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>1.07</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X18" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.56%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>四川省-泸州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[23泸建01,23泸建02]</t>
+          <t>本期超短期融资券发行金额为10亿元,所募集资金10亿元拟用于偿还发行人到期债券23中兵投资MTN001本金[23中兵投资MTN001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华西证券股份有限公司,申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>泸州两江投资控股集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>泸州市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中兵投资管理有限责任公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26HPI03K</t>
+          <t>26润建股份CP004</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>246046.SH</t>
+          <t>042680310.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.78</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26.84</v>
+        <v>55.05</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25华能MTN001</t>
+          <t>26润建股份CP003</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>8.35Y</t>
+          <t>97D</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.9819</t>
+          <t>1.7469</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/1.9300</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司</t>
+          <t>润建股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 41.24</t>
+          <t>D- 0.87</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4459,7 +4463,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4473,63 +4477,59 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.9867</v>
+        <v>0.34</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.82%~1.86%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期短期融资券发行金额5亿元,拟全部用于公司本部及子公司偿还有息债务</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,兴业证券股份有限公司,西南证券股份有限公司,光大证券股份有限公司,长城证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>润建股份有限公司2026年度第四期短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4539,13 +4539,13 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2036-09-10</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4565,27 +4565,27 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>社会服务</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>通信服务</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>通信服务</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26中兵投资SCP002</t>
+          <t>26武汉农商行绿债01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4628,64 +4628,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682226.IB</t>
+          <t>222680022.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.53</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>31.49</v>
+        <v>37.94</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24中兵01</t>
+          <t>25武汉农商科创债(柜台)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>254D+2.00Y</t>
+          <t>4.01Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5406</t>
+          <t>1.6184</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.5100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>中兵投资管理有限责任公司</t>
+          <t>武汉农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.85</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>09-09 11:00</t>
+          <t>09-09 10:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4705,55 +4705,55 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>2.0</v>
-      </c>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.62%~1.72%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z20" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元,所募集资金10亿元拟用于偿还发行人到期债券23中兵投资MTN001本金[23中兵投资MTN001]</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,长江证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>中兵投资管理有限责任公司2026年度第二期超短期融资券</t>
+          <t>武汉农村商业银行股份有限公司2026年绿色金融债券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4773,53 +4773,53 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4847,29 +4847,27 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26润建股份CP004</t>
+          <t>26北部湾MTN007A</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-10 18:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>042680310.IB</t>
+          <t>102683566.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -4880,48 +4878,48 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.78</t>
+          <t>1.40 ~ 2.20</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>55.05</v>
+        <v>44.94</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26润建股份CP003</t>
+          <t>24北部湾MTN010</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>97D</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7469</t>
+          <t>1.8508</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>润建股份有限公司</t>
+          <t>广西北部湾国际港务集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>D- 0.87</t>
+          <t>C- 20.81</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4941,26 +4939,26 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.34</v>
+        <v>9.02</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.86%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
@@ -4971,23 +4969,23 @@
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行金额5亿元,拟全部用于公司本部及子公司偿还有息债务</t>
+          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，拟用于发行人偿还到期债务[23北部湾MTN004]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中信银行股份有限公司</t>
+          <t>国家开发银行,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -4997,7 +4995,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>润建股份有限公司2026年度第四期短期融资券</t>
+          <t>广西北部湾国际港务集团有限公司2026年度第七期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5007,78 +5005,78 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-09</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY21" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO21" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ21" s="3" t="inlineStr">
-        <is>
-          <t>社会服务</t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr">
-        <is>
-          <t>通信服务</t>
-        </is>
-      </c>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>通信服务</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr">
-        <is>
-          <t>通信设备</t>
-        </is>
-      </c>
-      <c r="AU21" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AZ21" s="3"/>
@@ -5086,7 +5084,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26武汉农商行绿债01</t>
+          <t>26厦门金租债02</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5096,49 +5094,49 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>222680022.IB</t>
+          <t>252680008.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.00</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>37.94</v>
+        <v>57.93</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25武汉农商科创债(柜台)</t>
+          <t>26厦门金租债01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.01Y</t>
+          <t>1.41Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6184</t>
+          <t>1.7543</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5148,12 +5146,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>武汉农村商业银行股份有限公司</t>
+          <t>厦门金融租赁有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>B- 38.33</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5163,7 +5161,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-09 10:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5176,47 +5174,49 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>5.2</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.62%~1.72%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+          <t>本期债券募集资金主要用于补充公司中长期资金,支持公司逐步增长的融资租赁规模,优化公司资产负债结构和期限结构,为公司提供稳定的中长期资金来源 ,增强债务稳定性。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,长江证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,招商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,渤海银行股份有限公司,天津银行股份有限公司,北京农村商业银行股份有限公司,富邦华一银行有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>其他金融债</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>武汉农村商业银行股份有限公司2026年绿色金融债券</t>
+          <t>厦门金融租赁有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2028-09-11</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5267,27 +5267,27 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>金融租赁</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5320,59 +5320,59 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26北部湾MTN007A</t>
+          <t>一航YK07</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-10 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683566.IB</t>
+          <t>246026.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>44.94</v>
+        <v>52.94</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>24北部湾MTN010</t>
+          <t>一航YK06</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>2.75Y+N</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8508</t>
+          <t>1.7944</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司</t>
+          <t>中交第一航务工程局有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 20.81</t>
+          <t>C 27.07</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5411,17 +5411,17 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>9.02</v>
+        <v>3.5667</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5432,38 +5432,38 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为人民币0亿元，发行上限金额为人民币10亿元，拟用于发行人偿还到期债务[23北部湾MTN004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司债务[23一航Y1]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>国家开发银行,中国农业银行股份有限公司</t>
+          <t>西部证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾国际港务集团有限公司2026年度第七期中期票据(品种一)</t>
+          <t>中交第一航务工程局有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5479,12 +5479,12 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN23" s="3" t="inlineStr">
@@ -5499,27 +5499,27 @@
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AZ23" s="3"/>
@@ -5552,59 +5552,59 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26厦门金租债02</t>
+          <t>26上海农商01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 16:30</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>252680008.IB</t>
+          <t>2621003.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>57.93</v>
+        <v>32.94</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26厦门金租债01</t>
+          <t>25上海农商01(柜台)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.41Y</t>
+          <t>1.83Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7543</t>
+          <t>1.5136</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>厦门金融租赁有限公司</t>
+          <t>上海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 38.33</t>
+          <t>A 75.80</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5642,49 +5642,43 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U24" s="4" t="n">
-        <v>5.2</v>
-      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金主要用于补充公司中长期资金,支持公司逐步增长的融资租赁规模,优化公司资产负债结构和期限结构,为公司提供稳定的中长期资金来源 ,增强债务稳定性。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,招商银行股份有限公司,兴业银行股份有限公司,中国民生银行股份有限公司,渤海银行股份有限公司,天津银行股份有限公司,北京农村商业银行股份有限公司,富邦华一银行有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司</t>
+          <t>国泰海通证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海银行股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>其他金融债</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5699,7 +5693,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>厦门金融租赁有限公司2026年第二期金融债券</t>
+          <t>上海农村商业银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5709,7 +5703,7 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2028-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5735,27 +5729,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>金融租赁</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5788,7 +5782,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>一航YK07</t>
+          <t>26阳交02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5798,49 +5792,49 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>246026.SH</t>
+          <t>520471.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>52.94</v>
+        <v>54.03</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>一航YK06</t>
+          <t>26阳交01</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.75Y+N</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7944</t>
+          <t>1.8995</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5850,12 +5844,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>中交第一航务工程局有限公司</t>
+          <t>阳江市交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C 27.07</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5879,38 +5873,38 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.5667</v>
+        <v>3.35</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-阳江市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司债务[23一航Y1]</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将1亿元用于偿还有息债务,1亿元补充公司日常生产经营所需流动资金。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司,光大证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5921,33 +5915,33 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>中交第一航务工程局有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第三期)</t>
+          <t>阳江市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5962,27 +5956,27 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
@@ -6002,12 +5996,12 @@
       </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY25" s="3" t="inlineStr">
@@ -6020,17 +6014,17 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26上海农商01</t>
+          <t>26昆发01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:30</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2621003.IB</t>
+          <t>283922.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6039,40 +6033,40 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>30.0</v>
+        <v>7.2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>30.0</v>
+        <v>7.2</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>2.50 ~ 3.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.58</v>
+        <v>2.85</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>32.94</v>
+        <v>159.94</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>25上海农商01(柜台)</t>
+          <t>24昆发01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.83Y</t>
+          <t>278D</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5136</t>
+          <t>2.2654</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6082,12 +6076,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司</t>
+          <t>昆明发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>A 75.80</t>
+          <t>C- 21.70</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6097,7 +6091,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6107,46 +6101,48 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U26" s="3"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>2.5903</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.58%~1.68%</t>
+          <t>2.50%~2.60%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还“24昆发02”和“24昆发03”债券到期本金。[24昆发02,24昆发03]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国银行股份有限公司,中信银行股份有限公司,上海银行股份有限公司,申万宏源证券有限公司</t>
+          <t>太平洋证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6156,68 +6152,68 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>上海农村商业银行股份有限公司2026年金融债券(第一期)</t>
+          <t>昆明发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6250,7 +6246,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26阳交02</t>
+          <t>26驻产02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6260,7 +6256,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>520471.SZ</t>
+          <t>283874.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6269,40 +6265,40 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.0</v>
+        <v>3.24</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.0</v>
+        <v>3.24</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>54.03</v>
+        <v>71.03</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26阳交01</t>
+          <t>26驻产01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>4.54Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.8995</t>
+          <t>2.0825</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6312,12 +6308,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>阳江市交通投资集团有限公司</t>
+          <t>驻马店市产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 41.74</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6327,7 +6323,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6341,17 +6337,17 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>2.10%~2.20%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6362,17 +6358,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-阳江市</t>
+          <t>河南省-驻马店市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将1亿元用于偿还有息债务,1亿元补充公司日常生产经营所需流动资金。</t>
+          <t>本次债券发行金额为不超过人民币3.24亿元(含3.24亿元),扣除发行费用后,计划全部用于偿还到期的公司债券本金。[23驻产06]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,光大证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6388,12 +6384,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>阳江市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>驻马店市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6409,7 +6405,7 @@
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6432,21 +6428,9 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AQ27" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR27" s="3" t="inlineStr">
-        <is>
-          <t>综合交运基础设施</t>
-        </is>
-      </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>综合交运基础设施</t>
-        </is>
-      </c>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="3"/>
       <c r="AT27" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -6482,59 +6466,59 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26东航SCP003</t>
+          <t>26昆北01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>012682224.IB</t>
+          <t>283863.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12.49</v>
+        <v>61.03</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25东航MTN001</t>
+          <t>26沪苏01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>4.69Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5879</t>
+          <t>1.9175</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6544,12 +6528,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司</t>
+          <t>昆山北部新城集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 29.41</t>
+          <t>D- 1.50</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6559,7 +6543,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6569,119 +6553,119 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>1.2833</v>
+        <v>2.35</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
+          <t>本期债券募集资金拟全部用于偿还公司债券本金[24昆北01]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,杭州银行股份有限公司,南京银行股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空集团有限公司2026年度第三期超短期融资券</t>
+          <t>昆山北部新城集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2027-04-08</t>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5*无效</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>环保工程及服务</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6714,74 +6698,74 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26京能租赁CP002</t>
+          <t>26首科K1</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 18:30</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>042680311.IB</t>
+          <t>246005.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.9Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.37 ~ 1.57</t>
+          <t>1.60 ~ 2.80</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26.09</v>
+        <v>38.03</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26京能租赁CP001</t>
+          <t>25首科01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>219D</t>
+          <t>4.19Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.5290</t>
+          <t>2.0196</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.5900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>北京京能融资租赁有限公司</t>
+          <t>北京首都科技发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>D- 2.71</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6791,7 +6775,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6805,27 +6789,29 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.26</v>
-      </c>
+        <v>3.77</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.99%~2.09%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -6833,18 +6819,22 @@
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本次短期融资券拟募集资金5亿元,拟全部用于偿还发行人存量有息债务。</t>
+          <t>本次债券拟使用不超过3.00亿元用于支持科技创新领域,具体通过直接投资、基金投资(出资)等方式。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD29" s="3"/>
+          <t>东方证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>湖北省融资担保集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6854,12 +6844,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>北京京能融资租赁有限公司2026年度第二期短期融资券</t>
+          <t>北京首都科技发展集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6869,13 +6859,13 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6895,7 +6885,7 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6905,17 +6895,17 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>商业物业经营</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6925,7 +6915,7 @@
       </c>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW29" s="3" t="inlineStr">
@@ -6948,59 +6938,59 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中远海运SCP004</t>
+          <t>26中金12</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682223.IB</t>
+          <t>246041.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>30.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.46</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>17.81</v>
+        <v>14.11</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>18远海05</t>
+          <t>26中金K4</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.16Y</t>
+          <t>4.86Y+2.00Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5740</t>
+          <t>1.6995</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7010,12 +7000,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 35.13</t>
+          <t>B- 43.06</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7025,7 +7015,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7035,11 +7025,11 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.0033</v>
+        <v>4.38</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
@@ -7049,7 +7039,7 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7057,41 +7047,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本次募集资金30亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及用于生产经营活动。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将10亿元用于置换公司债券本金,50亿元用于补充流动资金。[23中金F1]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,中信建投证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司2026年度第四期超短期融资券</t>
+          <t>中国国际金融股份有限公司2026年面向专业投资者公开发行公司债券(第六期)(品种二)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7101,58 +7095,58 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2034-09-11</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-11</t>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -7162,7 +7156,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7180,7 +7174,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN005(绿色)(取消发行)</t>
+          <t>26东航SCP003</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7190,58 +7184,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>DY102683576.IB</t>
+          <t>012682224.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>30.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>30.0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.18</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.30 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>12.49</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26南昌轨交MTN004(绿色)</t>
+          <t>25东航MTN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.66Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7778</t>
+          <t>1.5879</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司</t>
+          <t>中国东方航空集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.82</t>
+          <t>C 29.41</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7264,16 +7264,18 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>1.2833</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>2.21%~2.31%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7284,28 +7286,28 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江西省-南昌市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
+          <t>本期超短期融资券发行金额为30亿元，所募集资金拟用于本级和下属企业归还存量债务及补充营运资金。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司,杭州银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7315,7 +7317,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据(取消发行)</t>
+          <t>中国东方航空集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7325,7 +7327,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2036-09-10</t>
+          <t>2027-04-08</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7346,32 +7348,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7399,81 +7401,79 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AZ31" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ31" s="3"/>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26首科K1</t>
+          <t>26京能租赁CP002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:30</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246005.SH</t>
+          <t>042680311.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.9Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.80</t>
+          <t>1.37 ~ 1.57</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>38.03</v>
+        <v>26.09</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25首科01</t>
+          <t>26京能租赁CP001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>4.19Y</t>
+          <t>219D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.0196</t>
+          <t>1.5290</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>1.5900/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>北京首都科技发展集团有限公司</t>
+          <t>北京京能融资租赁有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D- 2.71</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7497,29 +7497,27 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>2.96</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.26</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.99%~2.09%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -7527,22 +7525,18 @@
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本次债券拟使用不超过3.00亿元用于支持科技创新领域,具体通过直接投资、基金投资(出资)等方式。</t>
+          <t>本次短期融资券拟募集资金5亿元,拟全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>湖北省融资担保集团有限责任公司</t>
-        </is>
-      </c>
+          <t>北京银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7552,12 +7546,12 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>北京首都科技发展集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>北京京能融资租赁有限公司2026年度第二期短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7567,13 +7561,13 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7593,7 +7587,7 @@
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
@@ -7603,17 +7597,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>商业物业经营</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7623,7 +7617,7 @@
       </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
@@ -7646,108 +7640,108 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26冀交Y4</t>
+          <t>26中远海运SCP004</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>283916.SH</t>
+          <t>012682223.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.0</v>
+        <v>30.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.0</v>
+        <v>30.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.20 ~ 1.46</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>50.94</v>
+        <v>17.81</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>18远海05</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2.16Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1.5740</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>中国远洋海运集团有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.13</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>09-09 09:00</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>24冀交Y3</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>2.85Y+N</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>1.8041</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>河北交通投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>C- 23.36</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>09-09 15:00</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.75</v>
+        <v>1.0033</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7758,101 +7752,101 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟使用8亿元用于偿还公司债券本金[23冀交05]</t>
+          <t>发行人拟将本次募集资金30亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及用于生产经营活动。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,财达证券股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>河北交通投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
+          <t>中国远洋海运集团有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-11</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>航运</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>航运</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>航运</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>高速公路</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7860,12 +7854,12 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7878,74 +7872,68 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26临交02</t>
+          <t>26南昌轨交MTN005(绿色)(取消发行)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>283893.SH</t>
+          <t>DY102683576.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>5.4</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>32.03</v>
-      </c>
+          <t>2.00 ~ 2.18</t>
+        </is>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26临平交通PPN004</t>
+          <t>26南昌轨交MTN004(绿色)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>4.66Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7378</t>
+          <t>1.7778</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7499/--</t>
+          <t>1.7900/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司</t>
+          <t>南昌轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 36.63</t>
+          <t>C+ 33.82</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7955,7 +7943,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7965,44 +7953,46 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>4.6481</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>江西省-南昌市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币5.4亿元(含5.4亿元)，扣除发行费用后，全部用于偿还到期公司债券本金[23临交03]</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金用于偿还有息债务[21南昌轨交MTN001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>招商银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8012,101 +8002,103 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>杭州临平交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南昌轨道交通集团有限公司2026年度第五期绿色中期票据(取消发行)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-11</t>
+          <t>2036-09-10</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY34" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-11</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW34" s="3" t="inlineStr">
-        <is>
-          <t>含权</t>
-        </is>
-      </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26中铜K3</t>
+          <t>26冀交Y4</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8116,12 +8108,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>246018.SH</t>
+          <t>283916.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -8132,48 +8124,48 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>41.84</v>
+        <v>50.94</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26中国铜业MTN005</t>
+          <t>24冀交Y3</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>2.85Y+N</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7852</t>
+          <t>1.8041</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.7400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中国铜业有限公司</t>
+          <t>河北交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B- 36.78</t>
+          <t>C- 23.36</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8183,7 +8175,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-09 16:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8197,17 +8189,17 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.04%~2.14%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8218,17 +8210,17 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还到期债务</t>
+          <t>本期债券募集资金拟使用8亿元用于偿还公司债券本金[23冀交05]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8239,7 +8231,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8249,23 +8241,23 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中国铜业有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)</t>
+          <t>河北交通投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2036-09-11</t>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -8280,32 +8272,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8320,12 +8312,12 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY35" s="3" t="inlineStr">
@@ -8338,7 +8330,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26联资06(取消发行)</t>
+          <t>26临交02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8348,58 +8340,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>DY283885.SH</t>
+          <t>283893.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>5.4</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>5.4</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>32.03</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24联投资本PPN003B</t>
+          <t>26临平交通PPN004</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8836</t>
+          <t>1.7378</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7499/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>湖北联投资本投资发展有限公司</t>
+          <t>杭州临平交通集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 19.60</t>
+          <t>B- 36.63</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8409,7 +8407,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8422,37 +8420,35 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>4.6481</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t>1.91%~2.01%</t>
-        </is>
-      </c>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X36" s="3"/>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>湖北省-武汉市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金0.10亿元用于偿还到期债务,3.90亿元用于补充公司流动资金。</t>
+          <t>本期债券发行总额不超过人民币5.4亿元(含5.4亿元)，扣除发行费用后，全部用于偿还到期公司债券本金[23临交03]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8473,7 +8469,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>湖北联投资本投资发展有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)(取消发行)</t>
+          <t>杭州临平交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8494,7 +8490,7 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
@@ -8504,37 +8500,37 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-11</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8544,7 +8540,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8562,7 +8558,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26江国03</t>
+          <t>26中铜K3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8572,64 +8568,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>283802.SH</t>
+          <t>246018.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.5</v>
+        <v>8.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>52.94</v>
+        <v>41.84</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24江阴国联PPN006</t>
+          <t>26中国铜业MTN005</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7841</t>
+          <t>1.7852</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7400</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>江阴市新国联集团有限公司</t>
+          <t>中国铜业有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 11.37</t>
+          <t>B- 36.78</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8639,7 +8635,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 16:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8649,21 +8645,21 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.04%~2.14%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8674,17 +8670,17 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23江国02]</t>
+          <t>本期债券募集资金拟全部用于偿还到期债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8695,7 +8691,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8705,63 +8701,63 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>江阴市新国联集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
+          <t>中国铜业有限公司2026年面向专业投资者公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2036-09-11</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8794,7 +8790,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26驻产02</t>
+          <t>26联资06(取消发行)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8804,7 +8800,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>283874.SH</t>
+          <t>DY283885.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8813,110 +8809,102 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>3.24</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>71.03</v>
-      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>24联投资本PPN003B</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>2.87Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.8836</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>湖北联投资本投资发展有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>C- 19.60</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>26驻产01</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>4.54Y</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>2.0825</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>2.1000/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>驻马店市产业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>B- 41.74</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>09-09 16:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U38" s="4" t="n">
-        <v>5.8</v>
-      </c>
+      <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.10%~2.20%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>河南省-驻马店市</t>
+          <t>湖北省-武汉市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行金额为不超过人民币3.24亿元(含3.24亿元),扣除发行费用后,计划全部用于偿还到期的公司债券本金。[23驻产06]</t>
+          <t>本期公司债券募集资金0.10亿元用于偿还到期债务,3.90亿元用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,光大证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8937,7 +8925,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>驻马店市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>湖北联投资本投资发展有限公司2026年面向专业投资者非公开发行公司债券(第三期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8953,7 +8941,7 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
@@ -8968,20 +8956,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3"/>
-      <c r="AR38" s="3"/>
-      <c r="AS38" s="3"/>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>金融控股</t>
+        </is>
+      </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9014,74 +9014,74 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP002</t>
+          <t>26江国03</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-09 18:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682221.IB</t>
+          <t>283802.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.0</v>
+        <v>3.5</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>18.31</v>
+        <v>52.94</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26南京公路SCP001</t>
+          <t>24江阴国联PPN006</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>241D</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.5252</t>
+          <t>1.7841</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.5800/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司</t>
+          <t>江阴市新国联集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 18.59</t>
+          <t>C- 11.37</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-09 09:00</t>
+          <t>09-09 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9105,50 +9105,44 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>3.0667</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23江国02]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>南京市交通建设投资控股(集团)有限责任公司</t>
-        </is>
-      </c>
+          <t>国金证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9158,33 +9152,33 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>南京公路发展(集团)有限公司2026年度第二期超短期融资券</t>
+          <t>江阴市新国联集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-06-07</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
@@ -9194,32 +9188,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9229,7 +9223,7 @@
       </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">
@@ -9252,74 +9246,74 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26江国04</t>
+          <t>26南京公路SCP002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>283803.SH</t>
+          <t>012682221.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.5</v>
+        <v>3.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>57.03</v>
+        <v>18.31</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26江阴国联PPN003</t>
+          <t>26南京公路SCP001</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>241D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.0499</t>
+          <t>1.5252</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>2.0400/--</t>
+          <t>1.5800/1.4900</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>江阴市新国联集团有限公司</t>
+          <t>南京公路发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 11.37</t>
+          <t>C- 18.59</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9329,7 +9323,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-09 15:00</t>
+          <t>09-09 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9343,44 +9337,50 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>5.1667</v>
-      </c>
-      <c r="V40" s="3"/>
+        <v>3.0667</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23江国02]</t>
+          <t>本期超短期融资券发行金额3亿元,本期发行的募集资金扣除发行费用后用于偿还发行人本级及下属子公司有息债务。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD40" s="3"/>
+          <t>中信银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr">
+        <is>
+          <t>南京市交通建设投资控股(集团)有限责任公司</t>
+        </is>
+      </c>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9390,33 +9390,33 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>江阴市新国联集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
+          <t>南京公路发展(集团)有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2027-06-07</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN40" s="3" t="inlineStr">
@@ -9426,32 +9426,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>综合公用</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="AV40" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW40" s="3" t="inlineStr">
@@ -9484,74 +9484,74 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26铸都01</t>
+          <t>26江国04</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-09 17:00</t>
+          <t>09-09 19:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>283839.SH</t>
+          <t>283803.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3</v>
+        <v>6.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>224.94</v>
+        <v>57.03</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25铸都02</t>
+          <t>26江阴国联PPN003</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.17Y</t>
+          <t>4.96Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.5842</t>
+          <t>2.0499</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>2.6600/2.4000</t>
+          <t>2.0400/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>嘉禾铸都发展集团有限公司</t>
+          <t>江阴市新国联集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.75</t>
+          <t>C- 11.37</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9575,45 +9575,41 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>1.07</v>
+        <v>5.1667</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>2.59%~2.69%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>湖南省-郴州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还“20嘉禾01”到期公司债券本金[20嘉禾01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还到期的公司债券本金[23江国02]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD41" s="3" t="inlineStr">
-        <is>
-          <t>嘉禾国投发展集团有限公司</t>
-        </is>
-      </c>
+          <t>国金证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9631,7 +9627,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>嘉禾铸都发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江阴市新国联集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9641,7 +9637,7 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9652,7 +9648,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9667,27 +9663,27 @@
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合公用</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9697,7 +9693,7 @@
       </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW41" s="3" t="inlineStr">
@@ -9720,134 +9716,134 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26国资01</t>
+          <t>26铸都01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-09 19:00</t>
+          <t>09-09 17:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283903.SH</t>
+          <t>283839.SH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8.0</v>
+        <v>0.3</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>8.0</v>
+        <v>0.3</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.50 ~ 3.50</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>32.03</v>
+        <v>224.94</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>25铸都02</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>2.17Y</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>2.5842</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>2.6600/2.4000</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>嘉禾铸都发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>C+ 34.75</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>09-09 15:00</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>25锡发K1</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>2.29Y</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>1.7290</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>安徽国元资本有限责任公司</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>D- 1.15</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>09-09 15:00</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>3.84</v>
+        <v>1.07</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.59%~2.69%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>湖南省-郴州市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将5.00亿元用于偿还公司债券本金(23资本01),剩余部分用于补充营运资金。[23资本01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还“20嘉禾01”到期公司债券本金[20嘉禾01]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3" t="inlineStr">
         <is>
-          <t>安徽国元金融控股集团有限责任公司</t>
+          <t>嘉禾国投发展集团有限公司</t>
         </is>
       </c>
       <c r="AE42" s="3" t="inlineStr">
@@ -9867,7 +9863,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>安徽国元资本有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>嘉禾铸都发展集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9877,7 +9873,7 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK42" s="3"/>
@@ -9888,7 +9884,7 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9898,37 +9894,37 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -9938,7 +9934,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9956,7 +9952,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26昆发01</t>
+          <t>26国资01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9966,64 +9962,64 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283922.SH</t>
+          <t>283903.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>7.2</v>
+        <v>8.0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>7.2</v>
+        <v>8.0</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>159.94</v>
+        <v>32.03</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>24昆发01</t>
+          <t>25锡发K1</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>278D</t>
+          <t>2.29Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2.2654</t>
+          <t>1.7290</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>2.2700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>昆明发展投资集团有限公司</t>
+          <t>安徽国元资本有限责任公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 21.70</t>
+          <t>D- 1.15</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10047,41 +10043,45 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>2.5903</v>
+        <v>3.84</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>2.50%~2.60%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还“24昆发02”和“24昆发03”债券到期本金。[24昆发02,24昆发03]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将5.00亿元用于偿还公司债券本金(23资本01),剩余部分用于补充营运资金。[23资本01]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>太平洋证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3"/>
+          <t>国元证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>安徽国元金融控股集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE43" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>昆明发展投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安徽国元资本有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10109,13 +10109,13 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10130,47 +10130,47 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
